--- a/data/trans_orig/P6901-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6901-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52670</t>
+          <t>53505</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68133</t>
+          <t>68110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20618</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29530</t>
+          <t>29434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78355</t>
+          <t>77919</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95235</t>
+          <t>95391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11198</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26661</t>
+          <t>25826</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16337</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33217</t>
+          <t>33653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93151</t>
+          <t>92688</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113839</t>
+          <t>114054</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34163</t>
+          <t>33971</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45871</t>
+          <t>46007</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>131284</t>
+          <t>130567</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156270</t>
+          <t>154974</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>77,96%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32142</t>
+          <t>31927</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52830</t>
+          <t>53293</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18634</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42507</t>
+          <t>43803</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>67493</t>
+          <t>68210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73605</t>
+          <t>75594</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92749</t>
+          <t>93390</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34630</t>
+          <t>34582</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43822</t>
+          <t>43723</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114255</t>
+          <t>113336</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133889</t>
+          <t>134283</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,82%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17195</t>
+          <t>16554</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36339</t>
+          <t>34350</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11903</t>
+          <t>11951</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22588</t>
+          <t>22194</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42222</t>
+          <t>43141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94164</t>
+          <t>93033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112869</t>
+          <t>113093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55792</t>
+          <t>55870</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73217</t>
+          <t>72532</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155742</t>
+          <t>155863</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>181171</t>
+          <t>181598</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24180</t>
+          <t>23956</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42885</t>
+          <t>44016</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15334</t>
+          <t>16019</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32759</t>
+          <t>32681</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44429</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>69858</t>
+          <t>69737</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>334550</t>
+          <t>335509</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>372165</t>
+          <t>372213</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>158216</t>
+          <t>158264</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>182869</t>
+          <t>183829</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>501482</t>
+          <t>501537</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>549421</t>
+          <t>546815</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>78,97%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100140</t>
+          <t>100092</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137755</t>
+          <t>136796</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37252</t>
+          <t>36292</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61905</t>
+          <t>61857</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143006</t>
+          <t>145612</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>190945</t>
+          <t>190890</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2012 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48844</t>
+          <t>49053</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64301</t>
+          <t>64593</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25823</t>
+          <t>25158</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34213</t>
+          <t>34194</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78017</t>
+          <t>78209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95860</t>
+          <t>96650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,61%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>13050</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28799</t>
+          <t>28590</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>10096</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17038</t>
+          <t>16248</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34881</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,73%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61341</t>
+          <t>60319</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78311</t>
+          <t>78310</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41390</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54903</t>
+          <t>54298</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108300</t>
+          <t>109082</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129264</t>
+          <t>129400</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,87%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>14641</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31610</t>
+          <t>32632</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19941</t>
+          <t>20023</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25018</t>
+          <t>24882</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45982</t>
+          <t>45200</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48994</t>
+          <t>48942</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65693</t>
+          <t>66449</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32469</t>
+          <t>31605</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45111</t>
+          <t>45068</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85443</t>
+          <t>86666</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106658</t>
+          <t>108090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30563</t>
+          <t>30615</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20510</t>
+          <t>21374</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25878</t>
+          <t>24446</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47093</t>
+          <t>45870</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49468</t>
+          <t>47371</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64433</t>
+          <t>63777</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38863</t>
+          <t>39128</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53846</t>
+          <t>53725</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92795</t>
+          <t>92497</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113896</t>
+          <t>114546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,95%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12969</t>
+          <t>13625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27934</t>
+          <t>30031</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>10371</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27603</t>
+          <t>26953</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48704</t>
+          <t>49002</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,63%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>226963</t>
+          <t>227282</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>260196</t>
+          <t>259495</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>153383</t>
+          <t>153048</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>178952</t>
+          <t>177544</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>389548</t>
+          <t>388400</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>431185</t>
+          <t>429377</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67358</t>
+          <t>68059</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>100591</t>
+          <t>100272</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34709</t>
+          <t>36117</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60278</t>
+          <t>60613</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>110029</t>
+          <t>111837</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>151666</t>
+          <t>152814</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32613</t>
+          <t>32663</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46201</t>
+          <t>46187</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20363</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28314</t>
+          <t>28325</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56420</t>
+          <t>57084</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72431</t>
+          <t>72999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,3%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22060</t>
+          <t>22010</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9552</t>
+          <t>9592</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>11589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28168</t>
+          <t>27504</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63483</t>
+          <t>62885</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81111</t>
+          <t>81363</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44003</t>
+          <t>43938</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54114</t>
+          <t>54457</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111323</t>
+          <t>110831</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>132181</t>
+          <t>131977</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15873</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33501</t>
+          <t>34099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20354</t>
+          <t>20558</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41212</t>
+          <t>41704</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79156</t>
+          <t>78764</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95490</t>
+          <t>95702</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48835</t>
+          <t>48516</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59926</t>
+          <t>60431</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131697</t>
+          <t>131674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152946</t>
+          <t>152994</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14445</t>
+          <t>14233</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30779</t>
+          <t>31171</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15912</t>
+          <t>16231</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21736</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42985</t>
+          <t>43008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50815</t>
+          <t>50599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69405</t>
+          <t>68103</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44598</t>
+          <t>44634</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58064</t>
+          <t>58242</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99506</t>
+          <t>101257</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122819</t>
+          <t>124512</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>80,59%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19005</t>
+          <t>20307</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37595</t>
+          <t>37811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>29981</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54987</t>
+          <t>53236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>34,46%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>243733</t>
+          <t>242826</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>277615</t>
+          <t>274945</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>171011</t>
+          <t>172284</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>192299</t>
+          <t>193490</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>423295</t>
+          <t>422810</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>464402</t>
+          <t>463700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72386</t>
+          <t>75056</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>106268</t>
+          <t>107175</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>22808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45287</t>
+          <t>44014</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>101897</t>
+          <t>102599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>143004</t>
+          <t>143489</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46435</t>
+          <t>46884</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61589</t>
+          <t>61685</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37838</t>
+          <t>37244</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48490</t>
+          <t>48050</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88337</t>
+          <t>89292</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107239</t>
+          <t>107047</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,03%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>9530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24331</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16843</t>
+          <t>17437</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18658</t>
+          <t>18850</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37560</t>
+          <t>36605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69880</t>
+          <t>70576</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90279</t>
+          <t>90293</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71191</t>
+          <t>70997</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84656</t>
+          <t>84712</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144611</t>
+          <t>145906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>168520</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>21690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42103</t>
+          <t>41407</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>14018</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27539</t>
+          <t>27733</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42192</t>
+          <t>40776</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66101</t>
+          <t>64806</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33946</t>
+          <t>33426</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47136</t>
+          <t>46841</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66711</t>
+          <t>67098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91291</t>
+          <t>91943</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105678</t>
+          <t>105707</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>137593</t>
+          <t>138210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21331</t>
+          <t>21851</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30197</t>
+          <t>29810</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14591</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46506</t>
+          <t>46477</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59700</t>
+          <t>60903</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79750</t>
+          <t>80166</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61416</t>
+          <t>60991</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83169</t>
+          <t>82773</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128926</t>
+          <t>127849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>156689</t>
+          <t>157713</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,96%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41330</t>
+          <t>40127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20727</t>
+          <t>21123</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42480</t>
+          <t>42905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48237</t>
+          <t>47213</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76000</t>
+          <t>77077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,61%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>229201</t>
+          <t>229067</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>264426</t>
+          <t>262543</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>256445</t>
+          <t>256929</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>297888</t>
+          <t>297664</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>498342</t>
+          <t>497433</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>553674</t>
+          <t>552447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75079</t>
+          <t>76962</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110304</t>
+          <t>110438</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56327</t>
+          <t>56551</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>97770</t>
+          <t>97286</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140046</t>
+          <t>141273</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>195378</t>
+          <t>196287</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
